--- a/result/ECT2_LUSC_Tables.xlsx
+++ b/result/ECT2_LUSC_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,18 +439,17 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -464,7 +464,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,17 +472,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
-        <v>96</v>
-      </c>
-      <c r="D3" t="n">
         <v>76</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.002</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
@@ -494,15 +490,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D4" t="n">
         <v>167</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,7 +506,6 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,17 +514,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D6" t="n">
         <v>70</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.304</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.124</t>
         </is>
       </c>
     </row>
@@ -543,15 +532,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>156</v>
-      </c>
-      <c r="D7" t="n">
         <v>173</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -562,7 +548,6 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,17 +556,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
-      </c>
-      <c r="D9" t="n">
         <v>128</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.629</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.319</t>
         </is>
       </c>
     </row>
@@ -592,15 +574,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
-      </c>
-      <c r="D10" t="n">
         <v>70</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -609,15 +588,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D11" t="n">
         <v>40</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -626,15 +602,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -645,7 +618,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -654,17 +626,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="C14" t="n">
-        <v>168</v>
-      </c>
-      <c r="D14" t="n">
         <v>198</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.592</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.555</t>
         </is>
       </c>
     </row>
@@ -675,15 +644,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -694,7 +660,6 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -703,17 +668,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="C17" t="n">
-        <v>115</v>
-      </c>
-      <c r="D17" t="n">
         <v>164</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.181</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.088</t>
         </is>
       </c>
     </row>
@@ -724,15 +686,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
-      </c>
-      <c r="D18" t="n">
         <v>53</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -741,15 +700,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
-      </c>
-      <c r="D19" t="n">
         <v>19</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -758,15 +714,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -777,7 +730,6 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -786,17 +738,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
-      </c>
-      <c r="D22" t="n">
         <v>64</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.172</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.158</t>
         </is>
       </c>
     </row>
@@ -807,15 +756,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C23" t="n">
-        <v>125</v>
-      </c>
-      <c r="D23" t="n">
         <v>131</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -824,15 +770,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>30</v>
-      </c>
-      <c r="D24" t="n">
         <v>34</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -841,15 +784,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" t="n">
         <v>14</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -860,7 +800,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -869,17 +808,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
-      </c>
-      <c r="D27" t="n">
         <v>33</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.002</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.901</t>
         </is>
       </c>
     </row>
@@ -890,15 +826,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="C28" t="n">
-        <v>173</v>
-      </c>
-      <c r="D28" t="n">
         <v>211</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1745,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,6 +1694,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1772,11 +1715,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.044</t>
+        <v>1.023</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.022</t>
         </is>
       </c>
     </row>
@@ -1789,99 +1738,120 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.983</t>
+      <c r="C3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.887</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ECT2group_High</t>
+          <t>ECT2group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.331</t>
+        <v>1.327</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.081</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ECT2group_Low</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.929</t>
+        <v>1.306</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.160</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.246</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.217</t>
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.999</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>pathologic_stage_3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.712</t>
+        <v>1.372</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.068</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.131</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>pathologic_stage_4.0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.344</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.454</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.008</t>
+        <v>3.426</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.009</t>
         </is>
       </c>
     </row>
@@ -1896,18 +1866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1927,902 +1897,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.977</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0502</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>ECT2group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.077</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3.5160e-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3440.662</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2565.5277</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4315.7963</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>200.1873</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-30.1463</v>
-      </c>
-      <c r="D9" t="n">
-        <v>430.521</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.088</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>188.557</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-39.0847</v>
-      </c>
-      <c r="D10" t="n">
-        <v>416.1987</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.104</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>68.6254</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-214.9577</v>
-      </c>
-      <c r="D11" t="n">
-        <v>352.2086</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.634</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>131.396</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-682.1502</v>
-      </c>
-      <c r="D12" t="n">
-        <v>944.9422</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.751</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-21.974</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-34.1819</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-9.766</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.5208</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-3.7187</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.6771</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.749</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0589</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7.8048e-04</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3418.2031</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2556.9139</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4279.4922</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>165.1138</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-65.38120000000001</v>
-      </c>
-      <c r="D23" t="n">
-        <v>395.6088</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.160</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>290.7413</v>
-      </c>
-      <c r="C24" t="n">
-        <v>47.6057</v>
-      </c>
-      <c r="D24" t="n">
-        <v>533.8769</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.019</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>88.6567</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-251.1631</v>
-      </c>
-      <c r="D25" t="n">
-        <v>428.4765</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.608</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>82.672</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-462.0166</v>
-      </c>
-      <c r="D26" t="n">
-        <v>627.3606</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.766</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-22.9657</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-35.0045</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-10.9269</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.4465</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-3.6178</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.7248</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.782</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0571</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1.1881e-03</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3363.7642</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2485.7913</v>
-      </c>
-      <c r="D36" t="n">
-        <v>4241.7371</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>209.6842</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-18.9692</v>
-      </c>
-      <c r="D37" t="n">
-        <v>438.3375</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.072</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>259.9935</v>
-      </c>
-      <c r="C38" t="n">
-        <v>32.508</v>
-      </c>
-      <c r="D38" t="n">
-        <v>487.479</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>85.4007</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-299.4066</v>
-      </c>
-      <c r="D39" t="n">
-        <v>470.208</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>401.6101</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-477.1975</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1280.4177</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.369</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-21.2289</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-33.5354</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-8.9224</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-0.2551</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-3.4372</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.927</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0435</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6.5970e-03</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3425.2669</v>
-      </c>
-      <c r="C50" t="n">
-        <v>2476.0396</v>
-      </c>
-      <c r="D50" t="n">
-        <v>4374.4941</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>254.8013</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4.5348</v>
-      </c>
-      <c r="D51" t="n">
-        <v>505.0679</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>23.3991</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-777.3849</v>
-      </c>
-      <c r="D52" t="n">
-        <v>824.1831</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.954</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-20.7933</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-34.1982</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-7.3885</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-0.8375</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-4.3126</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.6376</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.636</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.928</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.130</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2835,6 +2012,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0431</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7.7787e-04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3541.6658</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2693.3478</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4389.9837</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>206.899</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-21.5126</v>
+      </c>
+      <c r="D9" t="n">
+        <v>435.3106</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-22.3975</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-34.4314</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-10.3636</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.5514</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-3.7285</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6258</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0502</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.5160e-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3440.662</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2565.5277</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4315.7963</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>200.1873</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-30.1463</v>
+      </c>
+      <c r="D20" t="n">
+        <v>430.521</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>188.557</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-39.0847</v>
+      </c>
+      <c r="D21" t="n">
+        <v>416.1987</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>68.6254</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-214.9577</v>
+      </c>
+      <c r="D22" t="n">
+        <v>352.2086</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>131.396</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-682.1502</v>
+      </c>
+      <c r="D23" t="n">
+        <v>944.9422</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.751</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-21.974</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-34.1819</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-9.766</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.5208</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-3.7187</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.6771</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.749</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0589</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7.8048e-04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3418.2031</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2556.9139</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4279.4922</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>165.1138</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-65.38120000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>395.6088</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.160</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>290.7413</v>
+      </c>
+      <c r="C35" t="n">
+        <v>47.6057</v>
+      </c>
+      <c r="D35" t="n">
+        <v>533.8769</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>88.6567</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-251.1631</v>
+      </c>
+      <c r="D36" t="n">
+        <v>428.4765</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.608</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>82.672</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-462.0166</v>
+      </c>
+      <c r="D37" t="n">
+        <v>627.3606</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-22.9657</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-35.0045</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-10.9269</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.4465</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-3.6178</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.7248</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.782</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0571</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.1881e-03</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3363.7642</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2485.7913</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4241.7371</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>209.6842</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-18.9692</v>
+      </c>
+      <c r="D48" t="n">
+        <v>438.3375</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>259.9935</v>
+      </c>
+      <c r="C49" t="n">
+        <v>32.508</v>
+      </c>
+      <c r="D49" t="n">
+        <v>487.479</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>85.4007</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-299.4066</v>
+      </c>
+      <c r="D50" t="n">
+        <v>470.208</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>401.6101</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-477.1975</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1280.4177</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.369</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-21.2289</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-33.5354</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-8.9224</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.2551</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-3.4372</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0435</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6.5970e-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3425.2669</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2476.0396</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4374.4941</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>254.8013</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.5348</v>
+      </c>
+      <c r="D62" t="n">
+        <v>505.0679</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>23.3991</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-777.3849</v>
+      </c>
+      <c r="D63" t="n">
+        <v>824.1831</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-20.7933</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-34.1982</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-7.3885</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.8375</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-4.3126</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2.6376</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/ECT2_LUSC_Tables.xlsx
+++ b/result/ECT2_LUSC_Tables.xlsx
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,12 @@
       <c r="B2" t="n">
         <v>1.023</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.003-1.044</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.022</t>
         </is>
@@ -1738,13 +1732,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.996-1.005</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.887</t>
         </is>
@@ -1759,13 +1752,12 @@
       <c r="B4" t="n">
         <v>1.327</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.825</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.965-1.825</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.081</t>
         </is>
@@ -1780,13 +1772,12 @@
       <c r="B5" t="n">
         <v>1.306</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.896</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.900-1.896</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.160</t>
         </is>
@@ -1801,13 +1792,12 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.444</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.693-1.444</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.999</t>
         </is>
@@ -1822,13 +1812,12 @@
       <c r="B7" t="n">
         <v>1.372</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.068</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.910-2.068</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.131</t>
         </is>
@@ -1843,13 +1832,12 @@
       <c r="B8" t="n">
         <v>3.426</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8.625</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.361-8.625</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.009</t>
         </is>
@@ -1866,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1870,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +1888,12 @@
       <c r="B2" t="n">
         <v>1.024</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.004</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.004-1.044</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.016</t>
         </is>
@@ -1926,13 +1908,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.995-1.005</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.977</t>
         </is>
@@ -1947,13 +1928,12 @@
       <c r="B4" t="n">
         <v>1.216</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.008-1.467</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.041</t>
         </is>
@@ -1968,13 +1948,12 @@
       <c r="B5" t="n">
         <v>1.329</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.970-1.820</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.077</t>
         </is>
@@ -1989,13 +1968,12 @@
       <c r="B6" t="n">
         <v>1.331</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.928</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.919-1.928</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.130</t>
         </is>
@@ -2012,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,15 +2006,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2050,7 +2023,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2065,7 +2037,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,7 +2051,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2095,7 +2065,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,7 +2079,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2121,7 +2089,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2130,15 +2097,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3541.6658</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2693.3478</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4389.9837</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>3541.666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2693.348-4389.984</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2153,13 +2119,12 @@
       <c r="B9" t="n">
         <v>206.899</v>
       </c>
-      <c r="C9" t="n">
-        <v>-21.5126</v>
-      </c>
-      <c r="D9" t="n">
-        <v>435.3106</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-21.513-435.311</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.076</t>
         </is>
@@ -2172,15 +2137,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-22.3975</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-34.4314</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-10.3636</v>
-      </c>
-      <c r="E10" t="inlineStr">
+        <v>-22.397</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-34.431--10.364</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2193,15 +2157,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5514</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-3.7285</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.6258</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>-0.551</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-3.729-2.626</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.733</t>
         </is>
@@ -2212,7 +2175,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2222,7 +2184,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2237,7 +2198,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2252,7 +2212,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2226,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,7 +2240,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,7 +2250,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2304,13 +2260,12 @@
       <c r="B19" t="n">
         <v>3440.662</v>
       </c>
-      <c r="C19" t="n">
-        <v>2565.5277</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4315.7963</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2565.528-4315.796</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2323,15 +2278,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>200.1873</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-30.1463</v>
-      </c>
-      <c r="D20" t="n">
-        <v>430.521</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>200.187</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-30.146-430.521</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.088</t>
         </is>
@@ -2346,13 +2300,12 @@
       <c r="B21" t="n">
         <v>188.557</v>
       </c>
-      <c r="C21" t="n">
-        <v>-39.0847</v>
-      </c>
-      <c r="D21" t="n">
-        <v>416.1987</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-39.085-416.199</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.104</t>
         </is>
@@ -2365,15 +2318,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>68.6254</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-214.9577</v>
-      </c>
-      <c r="D22" t="n">
-        <v>352.2086</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>68.625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-214.958-352.209</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.634</t>
         </is>
@@ -2388,13 +2340,12 @@
       <c r="B23" t="n">
         <v>131.396</v>
       </c>
-      <c r="C23" t="n">
-        <v>-682.1502</v>
-      </c>
-      <c r="D23" t="n">
-        <v>944.9422</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-682.15-944.942</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.751</t>
         </is>
@@ -2409,13 +2360,12 @@
       <c r="B24" t="n">
         <v>-21.974</v>
       </c>
-      <c r="C24" t="n">
-        <v>-34.1819</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-9.766</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-34.182--9.766</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2428,15 +2378,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5208</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-3.7187</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.6771</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>-0.521</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-3.719-2.677</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.749</t>
         </is>
@@ -2447,7 +2396,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2457,7 +2405,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2472,7 +2419,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2487,7 +2433,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,7 +2447,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2517,7 +2461,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2528,7 +2471,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2537,15 +2479,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3418.2031</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2556.9139</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4279.4922</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>3418.203</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2556.914-4279.492</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2558,15 +2499,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>165.1138</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-65.38120000000001</v>
-      </c>
-      <c r="D34" t="n">
-        <v>395.6088</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>165.114</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-65.381-395.609</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.160</t>
         </is>
@@ -2579,15 +2519,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>290.7413</v>
-      </c>
-      <c r="C35" t="n">
-        <v>47.6057</v>
-      </c>
-      <c r="D35" t="n">
-        <v>533.8769</v>
-      </c>
-      <c r="E35" t="inlineStr">
+        <v>290.741</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>47.606-533.877</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.019</t>
         </is>
@@ -2600,15 +2539,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>88.6567</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-251.1631</v>
-      </c>
-      <c r="D36" t="n">
-        <v>428.4765</v>
-      </c>
-      <c r="E36" t="inlineStr">
+        <v>88.657</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-251.163-428.477</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.608</t>
         </is>
@@ -2623,13 +2561,12 @@
       <c r="B37" t="n">
         <v>82.672</v>
       </c>
-      <c r="C37" t="n">
-        <v>-462.0166</v>
-      </c>
-      <c r="D37" t="n">
-        <v>627.3606</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-462.017-627.361</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.766</t>
         </is>
@@ -2642,15 +2579,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-22.9657</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-35.0045</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-10.9269</v>
-      </c>
-      <c r="E38" t="inlineStr">
+        <v>-22.966</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-35.004--10.927</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2663,15 +2599,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.4465</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-3.6178</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.7248</v>
-      </c>
-      <c r="E39" t="inlineStr">
+        <v>-0.446</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-3.618-2.725</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.782</t>
         </is>
@@ -2682,7 +2617,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2692,7 +2626,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2707,7 +2640,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +2654,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2737,7 +2668,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2752,7 +2682,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2763,7 +2692,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2772,15 +2700,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3363.7642</v>
-      </c>
-      <c r="C47" t="n">
-        <v>2485.7913</v>
-      </c>
-      <c r="D47" t="n">
-        <v>4241.7371</v>
-      </c>
-      <c r="E47" t="inlineStr">
+        <v>3363.764</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2485.791-4241.737</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2793,15 +2720,14 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>209.6842</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-18.9692</v>
-      </c>
-      <c r="D48" t="n">
-        <v>438.3375</v>
-      </c>
-      <c r="E48" t="inlineStr">
+        <v>209.684</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-18.969-438.337</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
@@ -2814,15 +2740,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>259.9935</v>
-      </c>
-      <c r="C49" t="n">
-        <v>32.508</v>
-      </c>
-      <c r="D49" t="n">
-        <v>487.479</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>259.994</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>32.508-487.479</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.025</t>
         </is>
@@ -2835,15 +2760,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>85.4007</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-299.4066</v>
-      </c>
-      <c r="D50" t="n">
-        <v>470.208</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>85.401</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-299.407-470.208</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.663</t>
         </is>
@@ -2856,15 +2780,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>401.6101</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-477.1975</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1280.4177</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>401.61</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-477.198-1280.418</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.369</t>
         </is>
@@ -2877,15 +2800,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-21.2289</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-33.5354</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-8.9224</v>
-      </c>
-      <c r="E52" t="inlineStr">
+        <v>-21.229</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-33.535--8.922</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2898,15 +2820,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2551</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-3.4372</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.927</v>
-      </c>
-      <c r="E53" t="inlineStr">
+        <v>-0.255</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-3.437-2.927</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.875</t>
         </is>
@@ -2917,7 +2838,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2927,7 +2847,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2942,7 +2861,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2957,7 +2875,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,7 +2889,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2987,7 +2903,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2998,7 +2913,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3007,15 +2921,14 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3425.2669</v>
-      </c>
-      <c r="C61" t="n">
-        <v>2476.0396</v>
-      </c>
-      <c r="D61" t="n">
-        <v>4374.4941</v>
-      </c>
-      <c r="E61" t="inlineStr">
+        <v>3425.267</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2476.04-4374.494</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -3028,15 +2941,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>254.8013</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4.5348</v>
-      </c>
-      <c r="D62" t="n">
-        <v>505.0679</v>
-      </c>
-      <c r="E62" t="inlineStr">
+        <v>254.801</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.535-505.068</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
@@ -3049,15 +2961,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>23.3991</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-777.3849</v>
-      </c>
-      <c r="D63" t="n">
-        <v>824.1831</v>
-      </c>
-      <c r="E63" t="inlineStr">
+        <v>23.399</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-777.385-824.183</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.954</t>
         </is>
@@ -3070,15 +2981,14 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-20.7933</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-34.1982</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-7.3885</v>
-      </c>
-      <c r="E64" t="inlineStr">
+        <v>-20.793</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-34.198--7.388</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.002</t>
         </is>
@@ -3091,15 +3001,14 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8375</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-4.3126</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2.6376</v>
-      </c>
-      <c r="E65" t="inlineStr">
+        <v>-0.837</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-4.313-2.638</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.636</t>
         </is>
@@ -3110,7 +3019,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
